--- a/MiniTemplate/Datas/base.xlsx
+++ b/MiniTemplate/Datas/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B771F4A-B68E-4F45-8CBF-578AA0037667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DB1D71-13BE-4DDE-A51E-86781899D83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -148,6 +148,18 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_secret_box_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星阵币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽奖货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_time_core_matrix_token]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -484,16 +496,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="64.125" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -533,7 +545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -553,7 +565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -573,7 +585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>101</v>
       </c>
@@ -590,7 +602,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>102</v>
       </c>
@@ -607,7 +619,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>103</v>
       </c>
@@ -624,7 +636,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>104</v>
       </c>
@@ -641,7 +653,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>105</v>
       </c>
@@ -658,12 +670,24 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>106</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
